--- a/재고수불26.04.02.xlsx
+++ b/재고수불26.04.02.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1741</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9250" uniqueCount="1813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9262" uniqueCount="1815">
   <si>
     <t>LOT번호</t>
   </si>
@@ -6029,6 +6029,14 @@
   </si>
   <si>
     <t>1.9-2.1 PCR 96.3%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건조감량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6514,7 +6522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1739"/>
+  <dimension ref="A1:N1741"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="5" customWidth="1"/>
@@ -66005,8 +66013,82 @@
         <v>18</v>
       </c>
     </row>
+    <row r="1740" spans="1:14" ht="30" customHeight="1">
+      <c r="A1740" s="3">
+        <v>1739</v>
+      </c>
+      <c r="B1740" s="5" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C1740" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D1740" s="3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="E1740" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="F1740" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1740" s="18"/>
+      <c r="H1740" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I1740" s="15">
+        <v>1039.8</v>
+      </c>
+      <c r="J1740" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K1740" s="8"/>
+      <c r="L1740" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:14" ht="30" customHeight="1">
+      <c r="A1741" s="3">
+        <v>1740</v>
+      </c>
+      <c r="B1741" s="5" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C1741" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D1741" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1741" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="F1741" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1741" s="18"/>
+      <c r="H1741" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I1741" s="15">
+        <v>1030</v>
+      </c>
+      <c r="J1741" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K1741" s="8"/>
+      <c r="L1741" s="12">
+        <v>4</v>
+      </c>
+      <c r="M1741" s="2">
+        <v>97</v>
+      </c>
+      <c r="N1741" s="2">
+        <v>98.74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1739"/>
+  <autoFilter ref="A1:L1741"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/재고수불26.04.02.xlsx
+++ b/재고수불26.04.02.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1759</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9262" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9353" uniqueCount="1837">
   <si>
     <t>LOT번호</t>
   </si>
@@ -6041,6 +6041,76 @@
   </si>
   <si>
     <t>2026.08.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검역시료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근 베타지니</t>
+  </si>
+  <si>
+    <t>922606ZA0</t>
+  </si>
+  <si>
+    <t>922607ZA0</t>
+  </si>
+  <si>
+    <t>922608ZA0</t>
+  </si>
+  <si>
+    <t>922609ZA0</t>
+  </si>
+  <si>
+    <t>922610ZA0</t>
+  </si>
+  <si>
+    <t>922613ZA0</t>
+  </si>
+  <si>
+    <t>922070ZA0</t>
+  </si>
+  <si>
+    <t>922071ZA0</t>
+  </si>
+  <si>
+    <t>922072ZA0</t>
+  </si>
+  <si>
+    <t>922073ZA0</t>
+  </si>
+  <si>
+    <t>922074ZA0</t>
+  </si>
+  <si>
+    <t>922075CL0</t>
+  </si>
+  <si>
+    <t>922426PE0</t>
+  </si>
+  <si>
+    <t>922427CL0</t>
+  </si>
+  <si>
+    <t>922425ZA0</t>
+  </si>
+  <si>
+    <t>922424CL0</t>
+  </si>
+  <si>
+    <t>922423CL0</t>
+  </si>
+  <si>
+    <t>수매입고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.14</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6522,7 +6592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1741"/>
+  <dimension ref="A1:N1759"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="5" customWidth="1"/>
@@ -49185,6 +49255,9 @@
       <c r="I1248" s="20">
         <v>10.4</v>
       </c>
+      <c r="L1248" s="12">
+        <v>8</v>
+      </c>
     </row>
     <row r="1249" spans="1:12" ht="30" customHeight="1">
       <c r="A1249" s="3">
@@ -49664,6 +49737,9 @@
       <c r="I1264" s="20">
         <v>4.0999999999999996</v>
       </c>
+      <c r="L1264" s="12">
+        <v>7</v>
+      </c>
     </row>
     <row r="1265" spans="1:14" ht="30" customHeight="1">
       <c r="A1265" s="3">
@@ -49849,6 +49925,9 @@
       </c>
       <c r="I1270" s="20">
         <v>1.2</v>
+      </c>
+      <c r="L1270" s="12">
+        <v>7</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="30" customHeight="1">
@@ -66087,8 +66166,589 @@
         <v>98.74</v>
       </c>
     </row>
+    <row r="1742" spans="1:14" ht="30" customHeight="1">
+      <c r="A1742" s="3">
+        <v>1741</v>
+      </c>
+      <c r="B1742" s="5" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C1742" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1742" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E1742" s="8" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1742" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1742" s="18"/>
+      <c r="H1742" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="I1742" s="15">
+        <v>9.07</v>
+      </c>
+      <c r="J1742" s="3"/>
+      <c r="K1742" s="8" t="s">
+        <v>1815</v>
+      </c>
+      <c r="L1742" s="12">
+        <v>8</v>
+      </c>
+      <c r="M1742" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:14" ht="30" customHeight="1">
+      <c r="A1743" s="3">
+        <v>1742</v>
+      </c>
+      <c r="B1743" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1743" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1743" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1743" s="9" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F1743" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1743" s="19">
+        <v>74.59</v>
+      </c>
+      <c r="H1743" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1743" s="20">
+        <v>74.59</v>
+      </c>
+      <c r="L1743" s="12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:14" ht="30" customHeight="1">
+      <c r="A1744" s="3">
+        <v>1743</v>
+      </c>
+      <c r="B1744" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1744" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1744" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1744" s="9" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F1744" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1744" s="19">
+        <v>34.729999999999997</v>
+      </c>
+      <c r="H1744" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1744" s="20">
+        <v>34.729999999999997</v>
+      </c>
+      <c r="L1744" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:12" ht="30" customHeight="1">
+      <c r="A1745" s="3">
+        <v>1744</v>
+      </c>
+      <c r="B1745" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1745" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1745" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1745" s="9" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F1745" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1745" s="19">
+        <v>28.81</v>
+      </c>
+      <c r="H1745" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1745" s="20">
+        <v>28.81</v>
+      </c>
+      <c r="L1745" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:12" ht="30" customHeight="1">
+      <c r="A1746" s="3">
+        <v>1745</v>
+      </c>
+      <c r="B1746" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1746" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1746" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1746" s="9" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F1746" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1746" s="19">
+        <v>42.9</v>
+      </c>
+      <c r="H1746" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1746" s="20">
+        <v>42.9</v>
+      </c>
+      <c r="L1746" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:12" ht="30" customHeight="1">
+      <c r="A1747" s="3">
+        <v>1746</v>
+      </c>
+      <c r="B1747" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1747" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1747" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1747" s="9" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F1747" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1747" s="19">
+        <v>78.28</v>
+      </c>
+      <c r="H1747" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1747" s="20">
+        <v>78.28</v>
+      </c>
+      <c r="L1747" s="12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:12" ht="30" customHeight="1">
+      <c r="A1748" s="3">
+        <v>1747</v>
+      </c>
+      <c r="B1748" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1748" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1748" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1748" s="9" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F1748" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1748" s="19">
+        <v>41.01</v>
+      </c>
+      <c r="H1748" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1748" s="20">
+        <v>41.01</v>
+      </c>
+      <c r="L1748" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:12" ht="30" customHeight="1">
+      <c r="A1749" s="3">
+        <v>1748</v>
+      </c>
+      <c r="B1749" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1749" s="9" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D1749" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1749" s="9" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F1749" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1749" s="19">
+        <v>99.69</v>
+      </c>
+      <c r="H1749" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1749" s="20">
+        <v>99.69</v>
+      </c>
+      <c r="L1749" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:12" ht="30" customHeight="1">
+      <c r="A1750" s="3">
+        <v>1749</v>
+      </c>
+      <c r="B1750" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1750" s="9" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D1750" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1750" s="9" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F1750" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1750" s="19">
+        <v>101.64</v>
+      </c>
+      <c r="H1750" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1750" s="20">
+        <v>101.64</v>
+      </c>
+      <c r="L1750" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:12" ht="30" customHeight="1">
+      <c r="A1751" s="3">
+        <v>1750</v>
+      </c>
+      <c r="B1751" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1751" s="9" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D1751" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1751" s="9" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F1751" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1751" s="19">
+        <v>46.61</v>
+      </c>
+      <c r="H1751" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1751" s="20">
+        <v>46.61</v>
+      </c>
+      <c r="L1751" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:12" ht="30" customHeight="1">
+      <c r="A1752" s="3">
+        <v>1751</v>
+      </c>
+      <c r="B1752" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1752" s="9" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D1752" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1752" s="9" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F1752" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1752" s="19">
+        <v>20.54</v>
+      </c>
+      <c r="H1752" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1752" s="20">
+        <v>20.54</v>
+      </c>
+      <c r="L1752" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:12" ht="30" customHeight="1">
+      <c r="A1753" s="3">
+        <v>1752</v>
+      </c>
+      <c r="B1753" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1753" s="9" t="s">
+        <v>1817</v>
+      </c>
+      <c r="D1753" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1753" s="9" t="s">
+        <v>1828</v>
+      </c>
+      <c r="F1753" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1753" s="19">
+        <v>131.52000000000001</v>
+      </c>
+      <c r="H1753" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1753" s="20">
+        <v>131.52000000000001</v>
+      </c>
+      <c r="L1753" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:12" ht="30" customHeight="1">
+      <c r="A1754" s="3">
+        <v>1753</v>
+      </c>
+      <c r="B1754" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1754" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="D1754" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1754" s="9" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F1754" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1754" s="19">
+        <v>353.5</v>
+      </c>
+      <c r="H1754" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1754" s="20">
+        <v>353.5</v>
+      </c>
+      <c r="L1754" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:12" ht="30" customHeight="1">
+      <c r="A1755" s="3">
+        <v>1754</v>
+      </c>
+      <c r="B1755" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1755" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="D1755" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1755" s="9" t="s">
+        <v>1830</v>
+      </c>
+      <c r="F1755" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1755" s="19">
+        <v>20</v>
+      </c>
+      <c r="H1755" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1755" s="20">
+        <v>20</v>
+      </c>
+      <c r="L1755" s="12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:12" ht="30" customHeight="1">
+      <c r="A1756" s="3">
+        <v>1755</v>
+      </c>
+      <c r="B1756" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1756" s="9" t="s">
+        <v>993</v>
+      </c>
+      <c r="D1756" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1756" s="9" t="s">
+        <v>1831</v>
+      </c>
+      <c r="F1756" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1756" s="19">
+        <v>214.5</v>
+      </c>
+      <c r="H1756" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1756" s="20">
+        <v>214.5</v>
+      </c>
+      <c r="L1756" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:12" ht="30" customHeight="1">
+      <c r="A1757" s="3">
+        <v>1756</v>
+      </c>
+      <c r="B1757" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1757" s="9" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D1757" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1757" s="9" t="s">
+        <v>1832</v>
+      </c>
+      <c r="F1757" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1757" s="19">
+        <v>50.45</v>
+      </c>
+      <c r="H1757" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1757" s="20">
+        <v>50.45</v>
+      </c>
+      <c r="L1757" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:12" ht="30" customHeight="1">
+      <c r="A1758" s="3">
+        <v>1757</v>
+      </c>
+      <c r="B1758" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1758" s="9" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D1758" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1758" s="9" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F1758" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1758" s="19">
+        <v>200</v>
+      </c>
+      <c r="H1758" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1758" s="20">
+        <v>200</v>
+      </c>
+      <c r="L1758" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:12" ht="30" customHeight="1">
+      <c r="A1759" s="3">
+        <v>1758</v>
+      </c>
+      <c r="B1759" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C1759" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D1759" s="5" t="s">
+        <v>1835</v>
+      </c>
+      <c r="E1759" s="9" t="s">
+        <v>1834</v>
+      </c>
+      <c r="F1759" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1759" s="19">
+        <v>301</v>
+      </c>
+      <c r="H1759" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1759" s="20">
+        <v>301</v>
+      </c>
+      <c r="L1759" s="12">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1741"/>
+  <autoFilter ref="A1:L1759"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/재고수불26.04.02.xlsx
+++ b/재고수불26.04.02.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1769</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9353" uniqueCount="1837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9407" uniqueCount="1847">
   <si>
     <t>LOT번호</t>
   </si>
@@ -5900,10 +5900,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>필리핀 베노람</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2026.08.10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6111,6 +6107,50 @@
   </si>
   <si>
     <t>2026.08.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검역취소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베트남 SVN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정선감량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610290P2KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610290P3KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5-1.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8-2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.18</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6592,7 +6632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1759"/>
+  <dimension ref="A1:N1769"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="5" customWidth="1"/>
@@ -6616,7 +6656,7 @@
         <v>1072</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1237</v>
@@ -36973,7 +37013,7 @@
         <v>1145</v>
       </c>
       <c r="K892" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="L892" s="12">
         <v>10</v>
@@ -39928,13 +39968,13 @@
         <v>975</v>
       </c>
       <c r="B976" s="5" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="C976" s="8" t="s">
         <v>737</v>
       </c>
       <c r="D976" s="3" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="E976" s="8" t="s">
         <v>741</v>
@@ -39950,7 +39990,7 @@
         <v>0</v>
       </c>
       <c r="J976" s="3" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="K976" s="8"/>
       <c r="L976" s="12">
@@ -39968,13 +40008,13 @@
         <v>976</v>
       </c>
       <c r="B977" s="5" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="C977" s="8" t="s">
         <v>737</v>
       </c>
       <c r="D977" s="3" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="E977" s="8" t="s">
         <v>742</v>
@@ -39990,7 +40030,7 @@
         <v>0</v>
       </c>
       <c r="J977" s="3" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="K977" s="8"/>
       <c r="L977" s="12">
@@ -40029,7 +40069,7 @@
         <v>230.9</v>
       </c>
       <c r="J978" s="5" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="L978" s="12">
         <v>5</v>
@@ -40068,7 +40108,7 @@
         <v>0</v>
       </c>
       <c r="J979" s="3" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="K979" s="8"/>
       <c r="L979" s="12">
@@ -40108,7 +40148,7 @@
         <v>0</v>
       </c>
       <c r="J980" s="3" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="K980" s="8"/>
       <c r="L980" s="12">
@@ -42852,7 +42892,7 @@
       </c>
       <c r="J1054" s="3"/>
       <c r="K1054" s="8" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="L1054" s="12">
         <v>1</v>
@@ -42892,7 +42932,7 @@
       </c>
       <c r="J1055" s="3"/>
       <c r="K1055" s="8" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="L1055" s="12">
         <v>2</v>
@@ -62498,7 +62538,7 @@
         <v>495</v>
       </c>
       <c r="D1635" s="5" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="E1635" s="9" t="s">
         <v>1547</v>
@@ -65175,7 +65215,7 @@
         <v>1712</v>
       </c>
       <c r="B1713" s="5" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1713" s="8" t="s">
         <v>94</v>
@@ -65198,7 +65238,7 @@
       </c>
       <c r="J1713" s="3"/>
       <c r="K1713" s="8" t="s">
-        <v>1779</v>
+        <v>1840</v>
       </c>
       <c r="L1713" s="12">
         <v>4</v>
@@ -65215,7 +65255,7 @@
         <v>1713</v>
       </c>
       <c r="B1714" s="5" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1714" s="8" t="s">
         <v>94</v>
@@ -65238,7 +65278,7 @@
       </c>
       <c r="J1714" s="3"/>
       <c r="K1714" s="8" t="s">
-        <v>1779</v>
+        <v>1840</v>
       </c>
       <c r="L1714" s="12">
         <v>5</v>
@@ -65255,13 +65295,13 @@
         <v>1714</v>
       </c>
       <c r="B1715" s="5" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1715" s="8" t="s">
         <v>641</v>
       </c>
       <c r="D1715" s="5" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="E1715" s="9" t="s">
         <v>1568</v>
@@ -65287,7 +65327,7 @@
         <v>1715</v>
       </c>
       <c r="B1716" s="5" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1716" s="8" t="s">
         <v>641</v>
@@ -65319,7 +65359,7 @@
         <v>1716</v>
       </c>
       <c r="B1717" s="5" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1717" s="8" t="s">
         <v>641</v>
@@ -65351,7 +65391,7 @@
         <v>1717</v>
       </c>
       <c r="B1718" s="5" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1718" s="8" t="s">
         <v>641</v>
@@ -65360,7 +65400,7 @@
         <v>1127</v>
       </c>
       <c r="E1718" s="9" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="F1718" s="8" t="s">
         <v>9</v>
@@ -65372,7 +65412,7 @@
         <v>395</v>
       </c>
       <c r="K1718" s="9" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="L1718" s="12">
         <v>4</v>
@@ -65383,7 +65423,7 @@
         <v>1718</v>
       </c>
       <c r="B1719" s="5" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="C1719" s="8" t="s">
         <v>641</v>
@@ -65392,7 +65432,7 @@
         <v>1127</v>
       </c>
       <c r="E1719" s="9" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="F1719" s="8" t="s">
         <v>9</v>
@@ -65404,7 +65444,7 @@
         <v>105.3</v>
       </c>
       <c r="K1719" s="9" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="L1719" s="12">
         <v>5</v>
@@ -65415,7 +65455,7 @@
         <v>1719</v>
       </c>
       <c r="B1720" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1720" s="8" t="s">
         <v>774</v>
@@ -65437,10 +65477,10 @@
         <v>0</v>
       </c>
       <c r="J1720" s="3" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="K1720" s="8" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="L1720" s="12">
         <v>2</v>
@@ -65457,7 +65497,7 @@
         <v>1720</v>
       </c>
       <c r="B1721" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1721" s="8" t="s">
         <v>774</v>
@@ -65479,10 +65519,10 @@
         <v>0</v>
       </c>
       <c r="J1721" s="3" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="K1721" s="8" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="L1721" s="12">
         <v>3</v>
@@ -65499,7 +65539,7 @@
         <v>1721</v>
       </c>
       <c r="B1722" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1722" s="9" t="s">
         <v>79</v>
@@ -65534,7 +65574,7 @@
         <v>1722</v>
       </c>
       <c r="B1723" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1723" s="9" t="s">
         <v>79</v>
@@ -65569,7 +65609,7 @@
         <v>1723</v>
       </c>
       <c r="B1724" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1724" s="9" t="s">
         <v>79</v>
@@ -65604,7 +65644,7 @@
         <v>1724</v>
       </c>
       <c r="B1725" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1725" s="9" t="s">
         <v>807</v>
@@ -65633,7 +65673,7 @@
         <v>1725</v>
       </c>
       <c r="B1726" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1726" s="9" t="s">
         <v>807</v>
@@ -65665,7 +65705,7 @@
         <v>1726</v>
       </c>
       <c r="B1727" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1727" s="8" t="s">
         <v>913</v>
@@ -65686,7 +65726,7 @@
         <v>0</v>
       </c>
       <c r="K1727" s="9" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="L1727" s="12">
         <v>4</v>
@@ -65700,7 +65740,7 @@
         <v>1727</v>
       </c>
       <c r="B1728" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1728" s="8" t="s">
         <v>450</v>
@@ -65732,7 +65772,7 @@
         <v>1728</v>
       </c>
       <c r="B1729" s="5" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="C1729" s="8" t="s">
         <v>450</v>
@@ -65755,7 +65795,7 @@
       </c>
       <c r="J1729" s="3"/>
       <c r="K1729" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="L1729" s="12">
         <v>8</v>
@@ -65772,7 +65812,7 @@
         <v>1729</v>
       </c>
       <c r="B1730" s="5" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="C1730" s="8" t="s">
         <v>439</v>
@@ -65812,7 +65852,7 @@
         <v>1730</v>
       </c>
       <c r="B1731" s="5" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="C1731" s="9" t="s">
         <v>1748</v>
@@ -65844,13 +65884,13 @@
         <v>1731</v>
       </c>
       <c r="B1732" s="5" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="C1732" s="9" t="s">
         <v>1748</v>
       </c>
       <c r="D1732" s="5" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="E1732" s="9" t="s">
         <v>1749</v>
@@ -65876,7 +65916,7 @@
         <v>1732</v>
       </c>
       <c r="B1733" s="5" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C1733" s="9" t="s">
         <v>618</v>
@@ -65897,7 +65937,7 @@
         <v>0</v>
       </c>
       <c r="K1733" s="9" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="L1733" s="12">
         <v>13</v>
@@ -65908,7 +65948,7 @@
         <v>1733</v>
       </c>
       <c r="B1734" s="5" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C1734" s="9" t="s">
         <v>618</v>
@@ -65929,7 +65969,7 @@
         <v>658.1</v>
       </c>
       <c r="K1734" s="9" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="L1734" s="12">
         <v>15</v>
@@ -65940,7 +65980,7 @@
         <v>1734</v>
       </c>
       <c r="B1735" s="5" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C1735" s="9" t="s">
         <v>618</v>
@@ -65961,7 +66001,7 @@
         <v>0</v>
       </c>
       <c r="K1735" s="9" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="L1735" s="12">
         <v>15</v>
@@ -65972,7 +66012,7 @@
         <v>1735</v>
       </c>
       <c r="B1736" s="5" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C1736" s="9" t="s">
         <v>618</v>
@@ -66001,16 +66041,16 @@
         <v>1736</v>
       </c>
       <c r="B1737" s="5" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C1737" s="9" t="s">
         <v>618</v>
       </c>
       <c r="D1737" s="5" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="E1737" s="9" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="F1737" s="8" t="s">
         <v>9</v>
@@ -66022,7 +66062,7 @@
         <v>956.9</v>
       </c>
       <c r="K1737" s="9" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="L1737" s="12">
         <v>16</v>
@@ -66033,16 +66073,16 @@
         <v>1737</v>
       </c>
       <c r="B1738" s="5" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C1738" s="9" t="s">
         <v>618</v>
       </c>
       <c r="D1738" s="5" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="E1738" s="9" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="F1738" s="8" t="s">
         <v>9</v>
@@ -66054,7 +66094,7 @@
         <v>114.1</v>
       </c>
       <c r="K1738" s="9" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="L1738" s="12">
         <v>17</v>
@@ -66065,7 +66105,7 @@
         <v>1738</v>
       </c>
       <c r="B1739" s="5" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C1739" s="9" t="s">
         <v>618</v>
@@ -66074,7 +66114,7 @@
         <v>1127</v>
       </c>
       <c r="E1739" s="9" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="F1739" s="8" t="s">
         <v>9</v>
@@ -66086,7 +66126,7 @@
         <v>544</v>
       </c>
       <c r="K1739" s="9" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="L1739" s="12">
         <v>18</v>
@@ -66097,13 +66137,13 @@
         <v>1739</v>
       </c>
       <c r="B1740" s="5" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C1740" s="8" t="s">
         <v>495</v>
       </c>
       <c r="D1740" s="3" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E1740" s="8" t="s">
         <v>500</v>
@@ -66131,7 +66171,7 @@
         <v>1740</v>
       </c>
       <c r="B1741" s="5" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C1741" s="8" t="s">
         <v>495</v>
@@ -66171,7 +66211,7 @@
         <v>1741</v>
       </c>
       <c r="B1742" s="5" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="C1742" s="8" t="s">
         <v>450</v>
@@ -66194,7 +66234,7 @@
       </c>
       <c r="J1742" s="3"/>
       <c r="K1742" s="8" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="L1742" s="12">
         <v>8</v>
@@ -66208,16 +66248,16 @@
         <v>1742</v>
       </c>
       <c r="B1743" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1743" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D1743" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1743" s="9" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="F1743" s="8" t="s">
         <v>9</v>
@@ -66240,16 +66280,16 @@
         <v>1743</v>
       </c>
       <c r="B1744" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1744" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D1744" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1744" s="9" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="F1744" s="8" t="s">
         <v>9</v>
@@ -66267,21 +66307,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1745" spans="1:12" ht="30" customHeight="1">
+    <row r="1745" spans="1:13" ht="30" customHeight="1">
       <c r="A1745" s="3">
         <v>1744</v>
       </c>
       <c r="B1745" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1745" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D1745" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1745" s="9" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="F1745" s="8" t="s">
         <v>9</v>
@@ -66299,21 +66339,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="1746" spans="1:12" ht="30" customHeight="1">
+    <row r="1746" spans="1:13" ht="30" customHeight="1">
       <c r="A1746" s="3">
         <v>1745</v>
       </c>
       <c r="B1746" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1746" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D1746" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1746" s="9" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="F1746" s="8" t="s">
         <v>9</v>
@@ -66331,21 +66371,21 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1747" spans="1:12" ht="30" customHeight="1">
+    <row r="1747" spans="1:13" ht="30" customHeight="1">
       <c r="A1747" s="3">
         <v>1746</v>
       </c>
       <c r="B1747" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1747" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D1747" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1747" s="9" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="F1747" s="8" t="s">
         <v>9</v>
@@ -66363,21 +66403,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="1748" spans="1:12" ht="30" customHeight="1">
+    <row r="1748" spans="1:13" ht="30" customHeight="1">
       <c r="A1748" s="3">
         <v>1747</v>
       </c>
       <c r="B1748" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1748" s="9" t="s">
         <v>283</v>
       </c>
       <c r="D1748" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1748" s="9" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="F1748" s="8" t="s">
         <v>9</v>
@@ -66395,21 +66435,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1749" spans="1:12" ht="30" customHeight="1">
+    <row r="1749" spans="1:13" ht="30" customHeight="1">
       <c r="A1749" s="3">
         <v>1748</v>
       </c>
       <c r="B1749" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1749" s="9" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="D1749" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1749" s="9" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="F1749" s="8" t="s">
         <v>9</v>
@@ -66427,21 +66467,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1750" spans="1:12" ht="30" customHeight="1">
+    <row r="1750" spans="1:13" ht="30" customHeight="1">
       <c r="A1750" s="3">
         <v>1749</v>
       </c>
       <c r="B1750" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1750" s="9" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="D1750" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1750" s="9" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="F1750" s="8" t="s">
         <v>9</v>
@@ -66459,21 +66499,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1751" spans="1:12" ht="30" customHeight="1">
+    <row r="1751" spans="1:13" ht="30" customHeight="1">
       <c r="A1751" s="3">
         <v>1750</v>
       </c>
       <c r="B1751" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1751" s="9" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="D1751" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1751" s="9" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="F1751" s="8" t="s">
         <v>9</v>
@@ -66491,21 +66531,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1752" spans="1:12" ht="30" customHeight="1">
+    <row r="1752" spans="1:13" ht="30" customHeight="1">
       <c r="A1752" s="3">
         <v>1751</v>
       </c>
       <c r="B1752" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1752" s="9" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="D1752" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1752" s="9" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="F1752" s="8" t="s">
         <v>9</v>
@@ -66523,21 +66563,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1753" spans="1:12" ht="30" customHeight="1">
+    <row r="1753" spans="1:13" ht="30" customHeight="1">
       <c r="A1753" s="3">
         <v>1752</v>
       </c>
       <c r="B1753" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1753" s="9" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="D1753" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1753" s="9" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="F1753" s="8" t="s">
         <v>9</v>
@@ -66555,21 +66595,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1754" spans="1:12" ht="30" customHeight="1">
+    <row r="1754" spans="1:13" ht="30" customHeight="1">
       <c r="A1754" s="3">
         <v>1753</v>
       </c>
       <c r="B1754" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1754" s="9" t="s">
         <v>800</v>
       </c>
       <c r="D1754" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1754" s="9" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="F1754" s="8" t="s">
         <v>9</v>
@@ -66587,21 +66627,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1755" spans="1:12" ht="30" customHeight="1">
+    <row r="1755" spans="1:13" ht="30" customHeight="1">
       <c r="A1755" s="3">
         <v>1754</v>
       </c>
       <c r="B1755" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1755" s="9" t="s">
         <v>869</v>
       </c>
       <c r="D1755" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1755" s="9" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="F1755" s="8" t="s">
         <v>9</v>
@@ -66619,21 +66659,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="1756" spans="1:12" ht="30" customHeight="1">
+    <row r="1756" spans="1:13" ht="30" customHeight="1">
       <c r="A1756" s="3">
         <v>1755</v>
       </c>
       <c r="B1756" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1756" s="9" t="s">
         <v>993</v>
       </c>
       <c r="D1756" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1756" s="9" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="F1756" s="8" t="s">
         <v>9</v>
@@ -66651,21 +66691,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1757" spans="1:12" ht="30" customHeight="1">
+    <row r="1757" spans="1:13" ht="30" customHeight="1">
       <c r="A1757" s="3">
         <v>1756</v>
       </c>
       <c r="B1757" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1757" s="9" t="s">
         <v>1016</v>
       </c>
       <c r="D1757" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1757" s="9" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="F1757" s="8" t="s">
         <v>9</v>
@@ -66683,21 +66723,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="1758" spans="1:12" ht="30" customHeight="1">
+    <row r="1758" spans="1:13" ht="30" customHeight="1">
       <c r="A1758" s="3">
         <v>1757</v>
       </c>
       <c r="B1758" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1758" s="9" t="s">
         <v>1025</v>
       </c>
       <c r="D1758" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1758" s="9" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="F1758" s="8" t="s">
         <v>9</v>
@@ -66715,21 +66755,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="1759" spans="1:12" ht="30" customHeight="1">
+    <row r="1759" spans="1:13" ht="30" customHeight="1">
       <c r="A1759" s="3">
         <v>1758</v>
       </c>
       <c r="B1759" s="5" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C1759" s="9" t="s">
         <v>1032</v>
       </c>
       <c r="D1759" s="5" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E1759" s="9" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="F1759" s="8" t="s">
         <v>9</v>
@@ -66747,8 +66787,336 @@
         <v>4</v>
       </c>
     </row>
+    <row r="1760" spans="1:13" ht="30" customHeight="1">
+      <c r="A1760" s="3">
+        <v>1759</v>
+      </c>
+      <c r="B1760" s="5" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C1760" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1760" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1760" s="9" t="s">
+        <v>1807</v>
+      </c>
+      <c r="F1760" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1760" s="20">
+        <v>162</v>
+      </c>
+      <c r="I1760" s="20">
+        <v>382</v>
+      </c>
+      <c r="J1760" s="5" t="s">
+        <v>1836</v>
+      </c>
+      <c r="L1760" s="12">
+        <v>18</v>
+      </c>
+      <c r="M1760" s="2">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:13" ht="30" customHeight="1">
+      <c r="A1761" s="3">
+        <v>1760</v>
+      </c>
+      <c r="B1761" s="5" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C1761" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="D1761" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1761" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="F1761" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1761" s="18"/>
+      <c r="H1761" s="15">
+        <v>35.5</v>
+      </c>
+      <c r="I1761" s="15">
+        <v>0</v>
+      </c>
+      <c r="J1761" s="3"/>
+      <c r="K1761" s="8"/>
+      <c r="L1761" s="12">
+        <v>1</v>
+      </c>
+      <c r="M1761" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:13" ht="30" customHeight="1">
+      <c r="A1762" s="3">
+        <v>1761</v>
+      </c>
+      <c r="B1762" s="5" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C1762" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1762" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E1762" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1762" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1762" s="18">
+        <v>0.03</v>
+      </c>
+      <c r="H1762" s="15"/>
+      <c r="I1762" s="15">
+        <v>51.16</v>
+      </c>
+      <c r="J1762" s="3"/>
+      <c r="K1762" s="8"/>
+      <c r="L1762" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:13" ht="30" customHeight="1">
+      <c r="A1763" s="3">
+        <v>1762</v>
+      </c>
+      <c r="B1763" s="5" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C1763" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1763" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E1763" s="8" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1763" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1763" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="H1763" s="15"/>
+      <c r="I1763" s="15">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="J1763" s="3"/>
+      <c r="K1763" s="8" t="s">
+        <v>1839</v>
+      </c>
+      <c r="L1763" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:13" ht="30" customHeight="1">
+      <c r="A1764" s="3">
+        <v>1763</v>
+      </c>
+      <c r="B1764" s="5" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C1764" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1764" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1764" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1764" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1764" s="18"/>
+      <c r="H1764" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="I1764" s="15">
+        <v>51.11</v>
+      </c>
+      <c r="J1764" s="3"/>
+      <c r="K1764" s="8"/>
+      <c r="L1764" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:13" ht="30" customHeight="1">
+      <c r="A1765" s="3">
+        <v>1764</v>
+      </c>
+      <c r="B1765" s="5" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1765" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1765" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1765" s="9" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F1765" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1765" s="20">
+        <v>0.8</v>
+      </c>
+      <c r="I1765" s="20">
+        <v>635.4</v>
+      </c>
+      <c r="K1765" s="9">
+        <v>46128</v>
+      </c>
+      <c r="L1765" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:13" ht="30" customHeight="1">
+      <c r="A1766" s="3">
+        <v>1765</v>
+      </c>
+      <c r="B1766" s="5" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1766" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1766" s="5" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E1766" s="9" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F1766" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1766" s="20">
+        <v>7.4</v>
+      </c>
+      <c r="I1766" s="20">
+        <v>628</v>
+      </c>
+      <c r="K1766" s="9">
+        <v>46128</v>
+      </c>
+      <c r="L1766" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:13" ht="30" customHeight="1">
+      <c r="A1767" s="3">
+        <v>1766</v>
+      </c>
+      <c r="B1767" s="5" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1767" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1767" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E1767" s="9" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F1767" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1767" s="20">
+        <v>628</v>
+      </c>
+      <c r="I1767" s="20">
+        <v>0</v>
+      </c>
+      <c r="K1767" s="9">
+        <v>46128</v>
+      </c>
+      <c r="L1767" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:13" ht="30" customHeight="1">
+      <c r="A1768" s="3">
+        <v>1767</v>
+      </c>
+      <c r="B1768" s="5" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1768" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1768" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1768" s="9" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F1768" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1768" s="19">
+        <v>424</v>
+      </c>
+      <c r="I1768" s="20">
+        <v>424</v>
+      </c>
+      <c r="K1768" s="9" t="s">
+        <v>1844</v>
+      </c>
+      <c r="L1768" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:13" ht="30" customHeight="1">
+      <c r="A1769" s="3">
+        <v>1768</v>
+      </c>
+      <c r="B1769" s="5" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C1769" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1769" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1769" s="9" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F1769" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1769" s="19">
+        <v>204</v>
+      </c>
+      <c r="I1769" s="20">
+        <v>204</v>
+      </c>
+      <c r="K1769" s="9" t="s">
+        <v>1845</v>
+      </c>
+      <c r="L1769" s="12">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1759"/>
+  <autoFilter ref="A1:L1769"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/재고수불26.04.02.xlsx
+++ b/재고수불26.04.02.xlsx
@@ -66827,7 +66827,7 @@
         <v>1760</v>
       </c>
       <c r="B1761" s="5" t="s">
-        <v>1610</v>
+        <v>1837</v>
       </c>
       <c r="C1761" s="8" t="s">
         <v>807</v>

--- a/재고수불26.04.02.xlsx
+++ b/재고수불26.04.02.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\excel_web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\skc_stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1769</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1779</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9407" uniqueCount="1847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9460" uniqueCount="1853">
   <si>
     <t>LOT번호</t>
   </si>
@@ -6004,11 +6004,137 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46127 P1 371kg 1.7이하 예상순도 52%</t>
+    <t>건조감량</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>정선입고</t>
+    <t>2026.08.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검역시료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근 베타지니</t>
+  </si>
+  <si>
+    <t>922606ZA0</t>
+  </si>
+  <si>
+    <t>922607ZA0</t>
+  </si>
+  <si>
+    <t>922608ZA0</t>
+  </si>
+  <si>
+    <t>922609ZA0</t>
+  </si>
+  <si>
+    <t>922610ZA0</t>
+  </si>
+  <si>
+    <t>922613ZA0</t>
+  </si>
+  <si>
+    <t>922070ZA0</t>
+  </si>
+  <si>
+    <t>922071ZA0</t>
+  </si>
+  <si>
+    <t>922072ZA0</t>
+  </si>
+  <si>
+    <t>922073ZA0</t>
+  </si>
+  <si>
+    <t>922074ZA0</t>
+  </si>
+  <si>
+    <t>922075CL0</t>
+  </si>
+  <si>
+    <t>922426PE0</t>
+  </si>
+  <si>
+    <t>922427CL0</t>
+  </si>
+  <si>
+    <t>922425ZA0</t>
+  </si>
+  <si>
+    <t>922424CL0</t>
+  </si>
+  <si>
+    <t>922423CL0</t>
+  </si>
+  <si>
+    <t>수매입고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검역취소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베트남 SVN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정선감량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610290P2KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610290P3KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5-1.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8-2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.08.19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610580P1KR0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.7이하 PCR 예상순도 52%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N610580P2KR0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6016,10 +6142,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>N610580P2KR0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.7-1.9 PCR 87.2%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6028,85 +6150,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.08.13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>건조감량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.08.13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검역시료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.08.13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근 베타지니</t>
-  </si>
-  <si>
-    <t>922606ZA0</t>
-  </si>
-  <si>
-    <t>922607ZA0</t>
-  </si>
-  <si>
-    <t>922608ZA0</t>
-  </si>
-  <si>
-    <t>922609ZA0</t>
-  </si>
-  <si>
-    <t>922610ZA0</t>
-  </si>
-  <si>
-    <t>922613ZA0</t>
-  </si>
-  <si>
-    <t>922070ZA0</t>
-  </si>
-  <si>
-    <t>922071ZA0</t>
-  </si>
-  <si>
-    <t>922072ZA0</t>
-  </si>
-  <si>
-    <t>922073ZA0</t>
-  </si>
-  <si>
-    <t>922074ZA0</t>
-  </si>
-  <si>
-    <t>922075CL0</t>
-  </si>
-  <si>
-    <t>922426PE0</t>
-  </si>
-  <si>
-    <t>922427CL0</t>
-  </si>
-  <si>
-    <t>922425ZA0</t>
-  </si>
-  <si>
-    <t>922424CL0</t>
-  </si>
-  <si>
-    <t>922423CL0</t>
-  </si>
-  <si>
-    <t>수매입고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.08.14</t>
+    <t>국내포장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6114,43 +6158,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.08.18</t>
+    <t>정선</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.08.18</t>
+    <t>N610010P2KR0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>검역취소</t>
+    <t>N610010P3KR0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>베트남 SVN</t>
+    <t>1.6-1.8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>정선감량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N610290P2KR0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>N610290P3KR0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.5-1.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.8-2.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.08.18</t>
+    <t>1.8-2.0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6282,7 +6306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6352,6 +6376,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -6632,7 +6659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1769"/>
+  <dimension ref="A1:N1779"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.77734375" style="5" customWidth="1"/>
@@ -47838,7 +47865,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="1201" spans="1:12" ht="30" customHeight="1">
+    <row r="1201" spans="1:14" ht="30" customHeight="1">
       <c r="A1201" s="3">
         <v>1200</v>
       </c>
@@ -47867,7 +47894,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="1202" spans="1:12" ht="30" customHeight="1">
+    <row r="1202" spans="1:14" ht="30" customHeight="1">
       <c r="A1202" s="3">
         <v>1201</v>
       </c>
@@ -47896,7 +47923,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="1203" spans="1:12" ht="30" customHeight="1">
+    <row r="1203" spans="1:14" ht="30" customHeight="1">
       <c r="A1203" s="3">
         <v>1202</v>
       </c>
@@ -47924,8 +47951,17 @@
       <c r="I1203" s="20">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="1204" spans="1:12" ht="30" customHeight="1">
+      <c r="L1203" s="12">
+        <v>5</v>
+      </c>
+      <c r="M1203" s="2">
+        <v>97</v>
+      </c>
+      <c r="N1203" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:14" ht="30" customHeight="1">
       <c r="A1204" s="3">
         <v>1203</v>
       </c>
@@ -47953,8 +47989,17 @@
       <c r="I1204" s="20">
         <v>11.1</v>
       </c>
-    </row>
-    <row r="1205" spans="1:12" ht="30" customHeight="1">
+      <c r="L1204" s="12">
+        <v>6</v>
+      </c>
+      <c r="M1204" s="2">
+        <v>98</v>
+      </c>
+      <c r="N1204" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:14" ht="30" customHeight="1">
       <c r="A1205" s="3">
         <v>1204</v>
       </c>
@@ -47982,8 +48027,17 @@
       <c r="I1205" s="20">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="1206" spans="1:12" ht="30" customHeight="1">
+      <c r="L1205" s="12">
+        <v>7</v>
+      </c>
+      <c r="M1205" s="2">
+        <v>98</v>
+      </c>
+      <c r="N1205" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:14" ht="30" customHeight="1">
       <c r="A1206" s="3">
         <v>1205</v>
       </c>
@@ -48012,7 +48066,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="1207" spans="1:12" ht="30" customHeight="1">
+    <row r="1207" spans="1:14" ht="30" customHeight="1">
       <c r="A1207" s="3">
         <v>1206</v>
       </c>
@@ -48041,7 +48095,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="1208" spans="1:12" ht="30" customHeight="1">
+    <row r="1208" spans="1:14" ht="30" customHeight="1">
       <c r="A1208" s="3">
         <v>1207</v>
       </c>
@@ -48070,7 +48124,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="1209" spans="1:12" ht="30" customHeight="1">
+    <row r="1209" spans="1:14" ht="30" customHeight="1">
       <c r="A1209" s="3">
         <v>1208</v>
       </c>
@@ -48099,7 +48153,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="1210" spans="1:12" ht="30" customHeight="1">
+    <row r="1210" spans="1:14" ht="30" customHeight="1">
       <c r="A1210" s="3">
         <v>1209</v>
       </c>
@@ -48128,7 +48182,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="1211" spans="1:12" ht="30" customHeight="1">
+    <row r="1211" spans="1:14" ht="30" customHeight="1">
       <c r="A1211" s="3">
         <v>1210</v>
       </c>
@@ -48157,7 +48211,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="1212" spans="1:12" ht="30" customHeight="1">
+    <row r="1212" spans="1:14" ht="30" customHeight="1">
       <c r="A1212" s="3">
         <v>1211</v>
       </c>
@@ -48186,7 +48240,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="1213" spans="1:12" ht="30" customHeight="1">
+    <row r="1213" spans="1:14" ht="30" customHeight="1">
       <c r="A1213" s="3">
         <v>1212</v>
       </c>
@@ -48215,7 +48269,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="1214" spans="1:12" ht="30" customHeight="1">
+    <row r="1214" spans="1:14" ht="30" customHeight="1">
       <c r="A1214" s="3">
         <v>1213</v>
       </c>
@@ -48247,7 +48301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="1215" spans="1:12" ht="30" customHeight="1">
+    <row r="1215" spans="1:14" ht="30" customHeight="1">
       <c r="A1215" s="3">
         <v>1214</v>
       </c>
@@ -48279,7 +48333,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1216" spans="1:12" ht="30" customHeight="1">
+    <row r="1216" spans="1:14" ht="30" customHeight="1">
       <c r="A1216" s="3">
         <v>1215</v>
       </c>
@@ -49149,6 +49203,9 @@
       </c>
       <c r="I1243" s="20">
         <v>8.1</v>
+      </c>
+      <c r="L1243" s="12">
+        <v>13</v>
       </c>
     </row>
     <row r="1244" spans="1:12" ht="30" customHeight="1">
@@ -56260,7 +56317,7 @@
         <v>1462</v>
       </c>
       <c r="L1450" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1451" spans="1:14" ht="30" customHeight="1">
@@ -58047,7 +58104,7 @@
         <v>1504</v>
       </c>
       <c r="L1501" s="12">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1502" spans="1:14" ht="30" customHeight="1">
@@ -58970,7 +59027,7 @@
         <v>1540</v>
       </c>
       <c r="L1527" s="12">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1528" spans="1:14" ht="30" customHeight="1">
@@ -65238,7 +65295,7 @@
       </c>
       <c r="J1713" s="3"/>
       <c r="K1713" s="8" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
       <c r="L1713" s="12">
         <v>4</v>
@@ -65278,7 +65335,7 @@
       </c>
       <c r="J1714" s="3"/>
       <c r="K1714" s="8" t="s">
-        <v>1840</v>
+        <v>1832</v>
       </c>
       <c r="L1714" s="12">
         <v>5</v>
@@ -65916,31 +65973,33 @@
         <v>1732</v>
       </c>
       <c r="B1733" s="5" t="s">
-        <v>1811</v>
-      </c>
-      <c r="C1733" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="D1733" s="5" t="s">
-        <v>1132</v>
-      </c>
-      <c r="E1733" s="9" t="s">
-        <v>1459</v>
+        <v>1806</v>
+      </c>
+      <c r="C1733" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D1733" s="3" t="s">
+        <v>1805</v>
+      </c>
+      <c r="E1733" s="8" t="s">
+        <v>500</v>
       </c>
       <c r="F1733" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H1733" s="20">
-        <v>346.8</v>
-      </c>
-      <c r="I1733" s="20">
-        <v>0</v>
-      </c>
-      <c r="K1733" s="9" t="s">
-        <v>1805</v>
-      </c>
+      <c r="G1733" s="18"/>
+      <c r="H1733" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="I1733" s="15">
+        <v>1039.8</v>
+      </c>
+      <c r="J1733" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K1733" s="8"/>
       <c r="L1733" s="12">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1734" spans="1:14" ht="30" customHeight="1">
@@ -65948,31 +66007,39 @@
         <v>1733</v>
       </c>
       <c r="B1734" s="5" t="s">
-        <v>1811</v>
-      </c>
-      <c r="C1734" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="D1734" s="5" t="s">
-        <v>1132</v>
-      </c>
-      <c r="E1734" s="9" t="s">
-        <v>1459</v>
+        <v>1806</v>
+      </c>
+      <c r="C1734" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D1734" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1734" s="8" t="s">
+        <v>500</v>
       </c>
       <c r="F1734" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H1734" s="20">
-        <v>53</v>
-      </c>
-      <c r="I1734" s="20">
-        <v>658.1</v>
-      </c>
-      <c r="K1734" s="9" t="s">
-        <v>1805</v>
-      </c>
+      <c r="G1734" s="18"/>
+      <c r="H1734" s="15">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I1734" s="15">
+        <v>1030</v>
+      </c>
+      <c r="J1734" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K1734" s="8"/>
       <c r="L1734" s="12">
-        <v>15</v>
+        <v>4</v>
+      </c>
+      <c r="M1734" s="2">
+        <v>97</v>
+      </c>
+      <c r="N1734" s="2">
+        <v>98.74</v>
       </c>
     </row>
     <row r="1735" spans="1:14" ht="30" customHeight="1">
@@ -65980,31 +66047,36 @@
         <v>1734</v>
       </c>
       <c r="B1735" s="5" t="s">
-        <v>1811</v>
-      </c>
-      <c r="C1735" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="D1735" s="5" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E1735" s="9" t="s">
-        <v>1459</v>
+        <v>1808</v>
+      </c>
+      <c r="C1735" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1735" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E1735" s="8" t="s">
+        <v>1776</v>
       </c>
       <c r="F1735" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H1735" s="20">
-        <v>658.1</v>
-      </c>
-      <c r="I1735" s="20">
-        <v>0</v>
-      </c>
-      <c r="K1735" s="9" t="s">
-        <v>1805</v>
+      <c r="G1735" s="18"/>
+      <c r="H1735" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="I1735" s="15">
+        <v>9.07</v>
+      </c>
+      <c r="J1735" s="3"/>
+      <c r="K1735" s="8" t="s">
+        <v>1807</v>
       </c>
       <c r="L1735" s="12">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="M1735" s="2">
+        <v>93</v>
       </c>
     </row>
     <row r="1736" spans="1:14" ht="30" customHeight="1">
@@ -66012,28 +66084,31 @@
         <v>1735</v>
       </c>
       <c r="B1736" s="5" t="s">
-        <v>1811</v>
+        <v>1828</v>
       </c>
       <c r="C1736" s="9" t="s">
-        <v>618</v>
+        <v>283</v>
       </c>
       <c r="D1736" s="5" t="s">
-        <v>1126</v>
+        <v>1827</v>
       </c>
       <c r="E1736" s="9" t="s">
-        <v>1459</v>
+        <v>1810</v>
       </c>
       <c r="F1736" s="8" t="s">
         <v>9</v>
       </c>
+      <c r="G1736" s="19">
+        <v>74.59</v>
+      </c>
       <c r="H1736" s="20">
-        <v>956.9</v>
+        <v>0</v>
       </c>
       <c r="I1736" s="20">
-        <v>0</v>
+        <v>74.59</v>
       </c>
       <c r="L1736" s="12">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1737" spans="1:14" ht="30" customHeight="1">
@@ -66041,31 +66116,31 @@
         <v>1736</v>
       </c>
       <c r="B1737" s="5" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C1737" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1737" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E1737" s="9" t="s">
         <v>1811</v>
       </c>
-      <c r="C1737" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="D1737" s="5" t="s">
-        <v>1806</v>
-      </c>
-      <c r="E1737" s="9" t="s">
-        <v>1808</v>
-      </c>
       <c r="F1737" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G1737" s="19">
-        <v>956.9</v>
+        <v>34.729999999999997</v>
+      </c>
+      <c r="H1737" s="20">
+        <v>0</v>
       </c>
       <c r="I1737" s="20">
-        <v>956.9</v>
-      </c>
-      <c r="K1737" s="9" t="s">
-        <v>1809</v>
+        <v>34.729999999999997</v>
       </c>
       <c r="L1737" s="12">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1738" spans="1:14" ht="30" customHeight="1">
@@ -66073,31 +66148,31 @@
         <v>1737</v>
       </c>
       <c r="B1738" s="5" t="s">
-        <v>1811</v>
+        <v>1828</v>
       </c>
       <c r="C1738" s="9" t="s">
-        <v>618</v>
+        <v>283</v>
       </c>
       <c r="D1738" s="5" t="s">
-        <v>1806</v>
+        <v>1827</v>
       </c>
       <c r="E1738" s="9" t="s">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="F1738" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G1738" s="19">
-        <v>114.1</v>
+        <v>28.81</v>
+      </c>
+      <c r="H1738" s="20">
+        <v>0</v>
       </c>
       <c r="I1738" s="20">
-        <v>114.1</v>
-      </c>
-      <c r="K1738" s="9" t="s">
-        <v>1809</v>
+        <v>28.81</v>
       </c>
       <c r="L1738" s="12">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1739" spans="1:14" ht="30" customHeight="1">
@@ -66105,31 +66180,31 @@
         <v>1738</v>
       </c>
       <c r="B1739" s="5" t="s">
-        <v>1811</v>
+        <v>1828</v>
       </c>
       <c r="C1739" s="9" t="s">
-        <v>618</v>
+        <v>283</v>
       </c>
       <c r="D1739" s="5" t="s">
-        <v>1127</v>
+        <v>1827</v>
       </c>
       <c r="E1739" s="9" t="s">
-        <v>1807</v>
+        <v>1813</v>
       </c>
       <c r="F1739" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G1739" s="19">
-        <v>544</v>
+        <v>42.9</v>
+      </c>
+      <c r="H1739" s="20">
+        <v>0</v>
       </c>
       <c r="I1739" s="20">
-        <v>544</v>
-      </c>
-      <c r="K1739" s="9" t="s">
-        <v>1810</v>
+        <v>42.9</v>
       </c>
       <c r="L1739" s="12">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1740" spans="1:14" ht="30" customHeight="1">
@@ -66137,33 +66212,31 @@
         <v>1739</v>
       </c>
       <c r="B1740" s="5" t="s">
-        <v>1813</v>
-      </c>
-      <c r="C1740" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="D1740" s="3" t="s">
-        <v>1812</v>
-      </c>
-      <c r="E1740" s="8" t="s">
-        <v>500</v>
+        <v>1828</v>
+      </c>
+      <c r="C1740" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1740" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E1740" s="9" t="s">
+        <v>1814</v>
       </c>
       <c r="F1740" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1740" s="18"/>
-      <c r="H1740" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="I1740" s="15">
-        <v>1039.8</v>
-      </c>
-      <c r="J1740" s="3" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K1740" s="8"/>
+      <c r="G1740" s="19">
+        <v>78.28</v>
+      </c>
+      <c r="H1740" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1740" s="20">
+        <v>78.28</v>
+      </c>
       <c r="L1740" s="12">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1741" spans="1:14" ht="30" customHeight="1">
@@ -66171,39 +66244,31 @@
         <v>1740</v>
       </c>
       <c r="B1741" s="5" t="s">
-        <v>1813</v>
-      </c>
-      <c r="C1741" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="D1741" s="3" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E1741" s="8" t="s">
-        <v>500</v>
+        <v>1828</v>
+      </c>
+      <c r="C1741" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1741" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E1741" s="9" t="s">
+        <v>1815</v>
       </c>
       <c r="F1741" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1741" s="18"/>
-      <c r="H1741" s="15">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="I1741" s="15">
-        <v>1030</v>
-      </c>
-      <c r="J1741" s="3" t="s">
-        <v>1088</v>
-      </c>
-      <c r="K1741" s="8"/>
+      <c r="G1741" s="19">
+        <v>41.01</v>
+      </c>
+      <c r="H1741" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1741" s="20">
+        <v>41.01</v>
+      </c>
       <c r="L1741" s="12">
-        <v>4</v>
-      </c>
-      <c r="M1741" s="2">
-        <v>97</v>
-      </c>
-      <c r="N1741" s="2">
-        <v>98.74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1742" spans="1:14" ht="30" customHeight="1">
@@ -66211,36 +66276,31 @@
         <v>1741</v>
       </c>
       <c r="B1742" s="5" t="s">
-        <v>1815</v>
-      </c>
-      <c r="C1742" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D1742" s="3" t="s">
-        <v>1134</v>
-      </c>
-      <c r="E1742" s="8" t="s">
-        <v>1776</v>
+        <v>1828</v>
+      </c>
+      <c r="C1742" s="9" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D1742" s="5" t="s">
+        <v>1827</v>
+      </c>
+      <c r="E1742" s="9" t="s">
+        <v>1816</v>
       </c>
       <c r="F1742" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1742" s="18"/>
-      <c r="H1742" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="I1742" s="15">
-        <v>9.07</v>
-      </c>
-      <c r="J1742" s="3"/>
-      <c r="K1742" s="8" t="s">
-        <v>1814</v>
+      <c r="G1742" s="19">
+        <v>99.69</v>
+      </c>
+      <c r="H1742" s="20">
+        <v>0</v>
+      </c>
+      <c r="I1742" s="20">
+        <v>99.69</v>
       </c>
       <c r="L1742" s="12">
-        <v>8</v>
-      </c>
-      <c r="M1742" s="2">
-        <v>93</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1743" spans="1:14" ht="30" customHeight="1">
@@ -66248,13 +66308,13 @@
         <v>1742</v>
       </c>
       <c r="B1743" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1743" s="9" t="s">
-        <v>283</v>
+        <v>1809</v>
       </c>
       <c r="D1743" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1743" s="9" t="s">
         <v>1817</v>
@@ -66263,16 +66323,16 @@
         <v>9</v>
       </c>
       <c r="G1743" s="19">
-        <v>74.59</v>
+        <v>101.64</v>
       </c>
       <c r="H1743" s="20">
         <v>0</v>
       </c>
       <c r="I1743" s="20">
-        <v>74.59</v>
+        <v>101.64</v>
       </c>
       <c r="L1743" s="12">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1744" spans="1:14" ht="30" customHeight="1">
@@ -66280,13 +66340,13 @@
         <v>1743</v>
       </c>
       <c r="B1744" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1744" s="9" t="s">
-        <v>283</v>
+        <v>1809</v>
       </c>
       <c r="D1744" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1744" s="9" t="s">
         <v>1818</v>
@@ -66295,16 +66355,16 @@
         <v>9</v>
       </c>
       <c r="G1744" s="19">
-        <v>34.729999999999997</v>
+        <v>46.61</v>
       </c>
       <c r="H1744" s="20">
         <v>0</v>
       </c>
       <c r="I1744" s="20">
-        <v>34.729999999999997</v>
+        <v>46.61</v>
       </c>
       <c r="L1744" s="12">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1745" spans="1:13" ht="30" customHeight="1">
@@ -66312,13 +66372,13 @@
         <v>1744</v>
       </c>
       <c r="B1745" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1745" s="9" t="s">
-        <v>283</v>
+        <v>1809</v>
       </c>
       <c r="D1745" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1745" s="9" t="s">
         <v>1819</v>
@@ -66327,16 +66387,16 @@
         <v>9</v>
       </c>
       <c r="G1745" s="19">
-        <v>28.81</v>
+        <v>20.54</v>
       </c>
       <c r="H1745" s="20">
         <v>0</v>
       </c>
       <c r="I1745" s="20">
-        <v>28.81</v>
+        <v>20.54</v>
       </c>
       <c r="L1745" s="12">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1746" spans="1:13" ht="30" customHeight="1">
@@ -66344,13 +66404,13 @@
         <v>1745</v>
       </c>
       <c r="B1746" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1746" s="9" t="s">
-        <v>283</v>
+        <v>1809</v>
       </c>
       <c r="D1746" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1746" s="9" t="s">
         <v>1820</v>
@@ -66359,16 +66419,16 @@
         <v>9</v>
       </c>
       <c r="G1746" s="19">
-        <v>42.9</v>
+        <v>131.52000000000001</v>
       </c>
       <c r="H1746" s="20">
         <v>0</v>
       </c>
       <c r="I1746" s="20">
-        <v>42.9</v>
+        <v>131.52000000000001</v>
       </c>
       <c r="L1746" s="12">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1747" spans="1:13" ht="30" customHeight="1">
@@ -66376,13 +66436,13 @@
         <v>1746</v>
       </c>
       <c r="B1747" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1747" s="9" t="s">
-        <v>283</v>
+        <v>800</v>
       </c>
       <c r="D1747" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1747" s="9" t="s">
         <v>1821</v>
@@ -66391,16 +66451,16 @@
         <v>9</v>
       </c>
       <c r="G1747" s="19">
-        <v>78.28</v>
+        <v>353.5</v>
       </c>
       <c r="H1747" s="20">
         <v>0</v>
       </c>
       <c r="I1747" s="20">
-        <v>78.28</v>
+        <v>353.5</v>
       </c>
       <c r="L1747" s="12">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1748" spans="1:13" ht="30" customHeight="1">
@@ -66408,13 +66468,13 @@
         <v>1747</v>
       </c>
       <c r="B1748" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1748" s="9" t="s">
-        <v>283</v>
+        <v>869</v>
       </c>
       <c r="D1748" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1748" s="9" t="s">
         <v>1822</v>
@@ -66423,16 +66483,16 @@
         <v>9</v>
       </c>
       <c r="G1748" s="19">
-        <v>41.01</v>
+        <v>20</v>
       </c>
       <c r="H1748" s="20">
         <v>0</v>
       </c>
       <c r="I1748" s="20">
-        <v>41.01</v>
+        <v>20</v>
       </c>
       <c r="L1748" s="12">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1749" spans="1:13" ht="30" customHeight="1">
@@ -66440,13 +66500,13 @@
         <v>1748</v>
       </c>
       <c r="B1749" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1749" s="9" t="s">
-        <v>1816</v>
+        <v>993</v>
       </c>
       <c r="D1749" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1749" s="9" t="s">
         <v>1823</v>
@@ -66455,16 +66515,16 @@
         <v>9</v>
       </c>
       <c r="G1749" s="19">
-        <v>99.69</v>
+        <v>214.5</v>
       </c>
       <c r="H1749" s="20">
         <v>0</v>
       </c>
       <c r="I1749" s="20">
-        <v>99.69</v>
+        <v>214.5</v>
       </c>
       <c r="L1749" s="12">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1750" spans="1:13" ht="30" customHeight="1">
@@ -66472,13 +66532,13 @@
         <v>1749</v>
       </c>
       <c r="B1750" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1750" s="9" t="s">
-        <v>1816</v>
+        <v>1016</v>
       </c>
       <c r="D1750" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1750" s="9" t="s">
         <v>1824</v>
@@ -66487,16 +66547,16 @@
         <v>9</v>
       </c>
       <c r="G1750" s="19">
-        <v>101.64</v>
+        <v>50.45</v>
       </c>
       <c r="H1750" s="20">
         <v>0</v>
       </c>
       <c r="I1750" s="20">
-        <v>101.64</v>
+        <v>50.45</v>
       </c>
       <c r="L1750" s="12">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1751" spans="1:13" ht="30" customHeight="1">
@@ -66504,13 +66564,13 @@
         <v>1750</v>
       </c>
       <c r="B1751" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1751" s="9" t="s">
-        <v>1816</v>
+        <v>1025</v>
       </c>
       <c r="D1751" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1751" s="9" t="s">
         <v>1825</v>
@@ -66519,16 +66579,16 @@
         <v>9</v>
       </c>
       <c r="G1751" s="19">
-        <v>46.61</v>
+        <v>200</v>
       </c>
       <c r="H1751" s="20">
         <v>0</v>
       </c>
       <c r="I1751" s="20">
-        <v>46.61</v>
+        <v>200</v>
       </c>
       <c r="L1751" s="12">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1752" spans="1:13" ht="30" customHeight="1">
@@ -66536,13 +66596,13 @@
         <v>1751</v>
       </c>
       <c r="B1752" s="5" t="s">
-        <v>1835</v>
+        <v>1828</v>
       </c>
       <c r="C1752" s="9" t="s">
-        <v>1816</v>
+        <v>1032</v>
       </c>
       <c r="D1752" s="5" t="s">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E1752" s="9" t="s">
         <v>1826</v>
@@ -66551,13 +66611,13 @@
         <v>9</v>
       </c>
       <c r="G1752" s="19">
-        <v>20.54</v>
+        <v>301</v>
       </c>
       <c r="H1752" s="20">
         <v>0</v>
       </c>
       <c r="I1752" s="20">
-        <v>20.54</v>
+        <v>301</v>
       </c>
       <c r="L1752" s="12">
         <v>4</v>
@@ -66568,31 +66628,34 @@
         <v>1752</v>
       </c>
       <c r="B1753" s="5" t="s">
-        <v>1835</v>
-      </c>
-      <c r="C1753" s="9" t="s">
-        <v>1816</v>
-      </c>
-      <c r="D1753" s="5" t="s">
-        <v>1834</v>
-      </c>
-      <c r="E1753" s="9" t="s">
-        <v>1827</v>
+        <v>1829</v>
+      </c>
+      <c r="C1753" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="D1753" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1753" s="8" t="s">
+        <v>809</v>
       </c>
       <c r="F1753" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1753" s="19">
-        <v>131.52000000000001</v>
-      </c>
-      <c r="H1753" s="20">
-        <v>0</v>
-      </c>
-      <c r="I1753" s="20">
-        <v>131.52000000000001</v>
-      </c>
+      <c r="G1753" s="18"/>
+      <c r="H1753" s="15">
+        <v>35.5</v>
+      </c>
+      <c r="I1753" s="15">
+        <v>0</v>
+      </c>
+      <c r="J1753" s="3"/>
+      <c r="K1753" s="8"/>
       <c r="L1753" s="12">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="M1753" s="2">
+        <v>90</v>
       </c>
     </row>
     <row r="1754" spans="1:13" ht="30" customHeight="1">
@@ -66600,31 +66663,31 @@
         <v>1753</v>
       </c>
       <c r="B1754" s="5" t="s">
-        <v>1835</v>
-      </c>
-      <c r="C1754" s="9" t="s">
-        <v>800</v>
-      </c>
-      <c r="D1754" s="5" t="s">
-        <v>1834</v>
-      </c>
-      <c r="E1754" s="9" t="s">
-        <v>1828</v>
+        <v>1830</v>
+      </c>
+      <c r="C1754" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1754" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E1754" s="8" t="s">
+        <v>98</v>
       </c>
       <c r="F1754" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1754" s="19">
-        <v>353.5</v>
-      </c>
-      <c r="H1754" s="20">
-        <v>0</v>
-      </c>
-      <c r="I1754" s="20">
-        <v>353.5</v>
-      </c>
+      <c r="G1754" s="18">
+        <v>0.03</v>
+      </c>
+      <c r="H1754" s="15"/>
+      <c r="I1754" s="15">
+        <v>51.16</v>
+      </c>
+      <c r="J1754" s="3"/>
+      <c r="K1754" s="8"/>
       <c r="L1754" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1755" spans="1:13" ht="30" customHeight="1">
@@ -66632,31 +66695,33 @@
         <v>1754</v>
       </c>
       <c r="B1755" s="5" t="s">
-        <v>1835</v>
-      </c>
-      <c r="C1755" s="9" t="s">
-        <v>869</v>
-      </c>
-      <c r="D1755" s="5" t="s">
-        <v>1834</v>
-      </c>
-      <c r="E1755" s="9" t="s">
-        <v>1829</v>
+        <v>1830</v>
+      </c>
+      <c r="C1755" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1755" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E1755" s="8" t="s">
+        <v>1776</v>
       </c>
       <c r="F1755" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1755" s="19">
-        <v>20</v>
-      </c>
-      <c r="H1755" s="20">
-        <v>0</v>
-      </c>
-      <c r="I1755" s="20">
-        <v>20</v>
+      <c r="G1755" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="H1755" s="15"/>
+      <c r="I1755" s="15">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="J1755" s="3"/>
+      <c r="K1755" s="8" t="s">
+        <v>1831</v>
       </c>
       <c r="L1755" s="12">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1756" spans="1:13" ht="30" customHeight="1">
@@ -66664,31 +66729,31 @@
         <v>1755</v>
       </c>
       <c r="B1756" s="5" t="s">
-        <v>1835</v>
-      </c>
-      <c r="C1756" s="9" t="s">
-        <v>993</v>
-      </c>
-      <c r="D1756" s="5" t="s">
-        <v>1834</v>
-      </c>
-      <c r="E1756" s="9" t="s">
         <v>1830</v>
       </c>
+      <c r="C1756" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1756" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1756" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="F1756" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1756" s="19">
-        <v>214.5</v>
-      </c>
-      <c r="H1756" s="20">
-        <v>0</v>
-      </c>
-      <c r="I1756" s="20">
-        <v>214.5</v>
-      </c>
+      <c r="G1756" s="18"/>
+      <c r="H1756" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="I1756" s="15">
+        <v>51.11</v>
+      </c>
+      <c r="J1756" s="3"/>
+      <c r="K1756" s="8"/>
       <c r="L1756" s="12">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1757" spans="1:13" ht="30" customHeight="1">
@@ -66696,31 +66761,31 @@
         <v>1756</v>
       </c>
       <c r="B1757" s="5" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="C1757" s="9" t="s">
-        <v>1016</v>
+        <v>791</v>
       </c>
       <c r="D1757" s="5" t="s">
-        <v>1834</v>
+        <v>1081</v>
       </c>
       <c r="E1757" s="9" t="s">
-        <v>1831</v>
+        <v>1458</v>
       </c>
       <c r="F1757" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1757" s="19">
-        <v>50.45</v>
-      </c>
       <c r="H1757" s="20">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I1757" s="20">
-        <v>50.45</v>
+        <v>635.4</v>
+      </c>
+      <c r="K1757" s="9">
+        <v>46128</v>
       </c>
       <c r="L1757" s="12">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1758" spans="1:13" ht="30" customHeight="1">
@@ -66728,31 +66793,31 @@
         <v>1757</v>
       </c>
       <c r="B1758" s="5" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="C1758" s="9" t="s">
-        <v>1025</v>
+        <v>791</v>
       </c>
       <c r="D1758" s="5" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="E1758" s="9" t="s">
-        <v>1832</v>
+        <v>1458</v>
       </c>
       <c r="F1758" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1758" s="19">
-        <v>200</v>
-      </c>
       <c r="H1758" s="20">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="I1758" s="20">
-        <v>200</v>
+        <v>628</v>
+      </c>
+      <c r="K1758" s="9">
+        <v>46128</v>
       </c>
       <c r="L1758" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1759" spans="1:13" ht="30" customHeight="1">
@@ -66760,31 +66825,31 @@
         <v>1758</v>
       </c>
       <c r="B1759" s="5" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="C1759" s="9" t="s">
-        <v>1032</v>
+        <v>791</v>
       </c>
       <c r="D1759" s="5" t="s">
-        <v>1834</v>
+        <v>1126</v>
       </c>
       <c r="E1759" s="9" t="s">
-        <v>1833</v>
+        <v>1458</v>
       </c>
       <c r="F1759" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1759" s="19">
-        <v>301</v>
-      </c>
       <c r="H1759" s="20">
-        <v>0</v>
+        <v>628</v>
       </c>
       <c r="I1759" s="20">
-        <v>301</v>
+        <v>0</v>
+      </c>
+      <c r="K1759" s="9">
+        <v>46128</v>
       </c>
       <c r="L1759" s="12">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1760" spans="1:13" ht="30" customHeight="1">
@@ -66792,331 +66857,657 @@
         <v>1759</v>
       </c>
       <c r="B1760" s="5" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="C1760" s="9" t="s">
-        <v>618</v>
+        <v>791</v>
       </c>
       <c r="D1760" s="5" t="s">
-        <v>1080</v>
+        <v>1127</v>
       </c>
       <c r="E1760" s="9" t="s">
-        <v>1807</v>
+        <v>1834</v>
       </c>
       <c r="F1760" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="H1760" s="20">
-        <v>162</v>
+      <c r="G1760" s="19">
+        <v>424</v>
       </c>
       <c r="I1760" s="20">
-        <v>382</v>
-      </c>
-      <c r="J1760" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="K1760" s="9" t="s">
         <v>1836</v>
       </c>
       <c r="L1760" s="12">
-        <v>18</v>
-      </c>
-      <c r="M1760" s="2">
-        <v>97.5</v>
-      </c>
-    </row>
-    <row r="1761" spans="1:13" ht="30" customHeight="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:14" ht="30" customHeight="1">
       <c r="A1761" s="3">
         <v>1760</v>
       </c>
       <c r="B1761" s="5" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C1761" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D1761" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1761" s="9" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F1761" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1761" s="19">
+        <v>204</v>
+      </c>
+      <c r="I1761" s="20">
+        <v>204</v>
+      </c>
+      <c r="K1761" s="9" t="s">
         <v>1837</v>
       </c>
-      <c r="C1761" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="D1761" s="3" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E1761" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="F1761" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1761" s="18"/>
-      <c r="H1761" s="15">
-        <v>35.5</v>
-      </c>
-      <c r="I1761" s="15">
-        <v>0</v>
-      </c>
-      <c r="J1761" s="3"/>
-      <c r="K1761" s="8"/>
       <c r="L1761" s="12">
-        <v>1</v>
-      </c>
-      <c r="M1761" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="1762" spans="1:13" ht="30" customHeight="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:14" ht="30" customHeight="1">
       <c r="A1762" s="3">
         <v>1761</v>
       </c>
       <c r="B1762" s="5" t="s">
-        <v>1838</v>
-      </c>
-      <c r="C1762" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1762" s="3" t="s">
-        <v>1254</v>
-      </c>
-      <c r="E1762" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1762" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1762" s="18">
-        <v>0.03</v>
-      </c>
-      <c r="H1762" s="15"/>
-      <c r="I1762" s="15">
-        <v>51.16</v>
-      </c>
-      <c r="J1762" s="3"/>
-      <c r="K1762" s="8"/>
+        <v>1839</v>
+      </c>
+      <c r="C1762" s="9" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D1762" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E1762" s="9" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F1762" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1762" s="20">
+        <v>1827.7</v>
+      </c>
+      <c r="I1762" s="20">
+        <v>1201.5</v>
+      </c>
       <c r="L1762" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="1763" spans="1:13" ht="30" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="M1762" s="2">
+        <v>94.5</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:14" ht="30" customHeight="1">
       <c r="A1763" s="3">
         <v>1762</v>
       </c>
       <c r="B1763" s="5" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="C1763" s="8" t="s">
-        <v>450</v>
+        <v>723</v>
       </c>
       <c r="D1763" s="3" t="s">
-        <v>1254</v>
+        <v>1080</v>
       </c>
       <c r="E1763" s="8" t="s">
-        <v>1776</v>
+        <v>1421</v>
       </c>
       <c r="F1763" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1763" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="H1763" s="15"/>
+        <v>1079</v>
+      </c>
+      <c r="G1763" s="18"/>
+      <c r="H1763" s="15">
+        <v>27.5</v>
+      </c>
       <c r="I1763" s="15">
-        <v>9.1199999999999992</v>
-      </c>
-      <c r="J1763" s="3"/>
-      <c r="K1763" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1763" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="K1763" s="8"/>
+      <c r="L1763" s="12">
+        <v>3</v>
+      </c>
+      <c r="M1763" s="2">
+        <v>100</v>
+      </c>
+      <c r="N1763" s="2">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:14" ht="30" customHeight="1">
+      <c r="A1764" s="3">
+        <v>1766</v>
+      </c>
+      <c r="B1764" s="5" t="s">
         <v>1839</v>
       </c>
-      <c r="L1763" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="1764" spans="1:13" ht="30" customHeight="1">
-      <c r="A1764" s="3">
-        <v>1763</v>
-      </c>
-      <c r="B1764" s="5" t="s">
-        <v>1838</v>
-      </c>
-      <c r="C1764" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1764" s="3" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E1764" s="8" t="s">
-        <v>98</v>
+      <c r="C1764" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1764" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1764" s="9" t="s">
+        <v>1459</v>
       </c>
       <c r="F1764" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G1764" s="18"/>
-      <c r="H1764" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="I1764" s="15">
-        <v>51.11</v>
-      </c>
-      <c r="J1764" s="3"/>
-      <c r="K1764" s="8"/>
+      <c r="H1764" s="20">
+        <v>200.8</v>
+      </c>
+      <c r="I1764" s="20">
+        <v>146</v>
+      </c>
+      <c r="K1764" s="9">
+        <v>46129</v>
+      </c>
       <c r="L1764" s="12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="1765" spans="1:13" ht="30" customHeight="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:14" ht="30" customHeight="1">
       <c r="A1765" s="3">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="B1765" s="5" t="s">
-        <v>1846</v>
+        <v>1839</v>
       </c>
       <c r="C1765" s="9" t="s">
-        <v>791</v>
+        <v>618</v>
       </c>
       <c r="D1765" s="5" t="s">
-        <v>1081</v>
+        <v>1126</v>
       </c>
       <c r="E1765" s="9" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="F1765" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H1765" s="20">
-        <v>0.8</v>
+        <v>146</v>
       </c>
       <c r="I1765" s="20">
-        <v>635.4</v>
+        <v>0</v>
       </c>
       <c r="K1765" s="9">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="L1765" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1766" spans="1:13" ht="30" customHeight="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:14" ht="30" customHeight="1">
       <c r="A1766" s="3">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="B1766" s="5" t="s">
-        <v>1846</v>
+        <v>1839</v>
       </c>
       <c r="C1766" s="9" t="s">
-        <v>791</v>
+        <v>618</v>
       </c>
       <c r="D1766" s="5" t="s">
-        <v>1841</v>
+        <v>1126</v>
       </c>
       <c r="E1766" s="9" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="F1766" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H1766" s="20">
-        <v>7.4</v>
+        <v>956.9</v>
       </c>
       <c r="I1766" s="20">
-        <v>628</v>
+        <v>0</v>
       </c>
       <c r="K1766" s="9">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="L1766" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1767" spans="1:13" ht="30" customHeight="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:14" ht="30" customHeight="1">
       <c r="A1767" s="3">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="B1767" s="5" t="s">
-        <v>1846</v>
+        <v>1839</v>
       </c>
       <c r="C1767" s="9" t="s">
-        <v>791</v>
+        <v>618</v>
       </c>
       <c r="D1767" s="5" t="s">
         <v>1126</v>
       </c>
       <c r="E1767" s="9" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="F1767" s="8" t="s">
         <v>9</v>
       </c>
       <c r="H1767" s="20">
-        <v>628</v>
+        <v>711.1</v>
       </c>
       <c r="I1767" s="20">
         <v>0</v>
       </c>
       <c r="K1767" s="9">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="L1767" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1768" spans="1:13" ht="30" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:14" ht="30" customHeight="1">
       <c r="A1768" s="3">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="B1768" s="5" t="s">
-        <v>1846</v>
+        <v>1839</v>
       </c>
       <c r="C1768" s="9" t="s">
-        <v>791</v>
+        <v>618</v>
       </c>
       <c r="D1768" s="5" t="s">
         <v>1127</v>
       </c>
       <c r="E1768" s="9" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="F1768" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G1768" s="19">
-        <v>424</v>
+        <v>198.1</v>
       </c>
       <c r="I1768" s="20">
-        <v>424</v>
+        <v>198.1</v>
       </c>
       <c r="K1768" s="9" t="s">
-        <v>1844</v>
+        <v>1841</v>
       </c>
       <c r="L1768" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1769" spans="1:13" ht="30" customHeight="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:14" ht="30" customHeight="1">
       <c r="A1769" s="3">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="B1769" s="5" t="s">
-        <v>1846</v>
+        <v>1839</v>
       </c>
       <c r="C1769" s="9" t="s">
-        <v>791</v>
+        <v>618</v>
       </c>
       <c r="D1769" s="5" t="s">
         <v>1127</v>
       </c>
       <c r="E1769" s="9" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F1769" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1769" s="19">
+        <v>0.9</v>
+      </c>
+      <c r="I1769" s="20">
+        <v>0.9</v>
+      </c>
+      <c r="K1769" s="9" t="s">
+        <v>1841</v>
+      </c>
+      <c r="L1769" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:14" ht="30" customHeight="1">
+      <c r="A1770" s="3">
+        <v>1772</v>
+      </c>
+      <c r="B1770" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1770" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1770" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1770" s="9" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F1770" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1770" s="19">
+        <v>956</v>
+      </c>
+      <c r="I1770" s="20">
+        <v>956</v>
+      </c>
+      <c r="K1770" s="9" t="s">
+        <v>1844</v>
+      </c>
+      <c r="L1770" s="12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:14" ht="30" customHeight="1">
+      <c r="A1771" s="3">
+        <v>1773</v>
+      </c>
+      <c r="B1771" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1771" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1771" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1771" s="9" t="s">
+        <v>1842</v>
+      </c>
+      <c r="F1771" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1771" s="19">
+        <v>115</v>
+      </c>
+      <c r="I1771" s="20">
+        <v>115</v>
+      </c>
+      <c r="K1771" s="9" t="s">
+        <v>1844</v>
+      </c>
+      <c r="L1771" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:14" ht="30" customHeight="1">
+      <c r="A1772" s="3">
+        <v>1774</v>
+      </c>
+      <c r="B1772" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1772" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1772" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1772" s="9" t="s">
         <v>1843</v>
       </c>
-      <c r="F1769" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1769" s="19">
-        <v>204</v>
-      </c>
-      <c r="I1769" s="20">
-        <v>204</v>
-      </c>
-      <c r="K1769" s="9" t="s">
+      <c r="F1772" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1772" s="19">
+        <v>382</v>
+      </c>
+      <c r="I1772" s="20">
+        <v>382</v>
+      </c>
+      <c r="K1772" s="9" t="s">
         <v>1845</v>
       </c>
-      <c r="L1769" s="12">
-        <v>13</v>
+      <c r="L1772" s="12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:14" ht="30" customHeight="1">
+      <c r="A1773" s="3">
+        <v>1775</v>
+      </c>
+      <c r="B1773" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1773" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1773" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1773" s="9" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F1773" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1773" s="19">
+        <v>162</v>
+      </c>
+      <c r="I1773" s="20">
+        <v>162</v>
+      </c>
+      <c r="K1773" s="9" t="s">
+        <v>1845</v>
+      </c>
+      <c r="L1773" s="12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:14" ht="30" customHeight="1">
+      <c r="A1774" s="25">
+        <v>1776</v>
+      </c>
+      <c r="B1774" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1774" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1774" s="5" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E1774" s="9" t="s">
+        <v>1843</v>
+      </c>
+      <c r="F1774" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1774" s="20">
+        <v>162</v>
+      </c>
+      <c r="I1774" s="20">
+        <v>0</v>
+      </c>
+      <c r="J1774" s="5" t="s">
+        <v>1847</v>
+      </c>
+      <c r="L1774" s="12">
+        <v>22</v>
+      </c>
+      <c r="M1774" s="2">
+        <v>97.5</v>
+      </c>
+      <c r="N1774" s="2">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:14" ht="30" customHeight="1">
+      <c r="A1775" s="3">
+        <v>1777</v>
+      </c>
+      <c r="B1775" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1775" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="D1775" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E1775" s="9" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F1775" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1775" s="20">
+        <v>2.64</v>
+      </c>
+      <c r="I1775" s="20">
+        <v>78.56</v>
+      </c>
+      <c r="K1775" s="9">
+        <v>46130</v>
+      </c>
+      <c r="L1775" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:14" ht="30" customHeight="1">
+      <c r="A1776" s="3">
+        <v>1778</v>
+      </c>
+      <c r="B1776" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1776" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="D1776" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E1776" s="9" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F1776" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1776" s="20">
+        <v>11.76</v>
+      </c>
+      <c r="I1776" s="20">
+        <v>66.8</v>
+      </c>
+      <c r="K1776" s="9">
+        <v>46130</v>
+      </c>
+      <c r="L1776" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:12" ht="30" customHeight="1">
+      <c r="A1777" s="3">
+        <v>1779</v>
+      </c>
+      <c r="B1777" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1777" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="D1777" s="5" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E1777" s="9" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F1777" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1777" s="20">
+        <v>66.8</v>
+      </c>
+      <c r="I1777" s="20">
+        <v>0</v>
+      </c>
+      <c r="K1777" s="9">
+        <v>46130</v>
+      </c>
+      <c r="L1777" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:12" ht="30" customHeight="1">
+      <c r="A1778" s="3">
+        <v>1780</v>
+      </c>
+      <c r="B1778" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1778" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="D1778" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1778" s="9" t="s">
+        <v>1849</v>
+      </c>
+      <c r="F1778" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1778" s="19">
+        <v>58.28</v>
+      </c>
+      <c r="I1778" s="20">
+        <v>58.28</v>
+      </c>
+      <c r="K1778" s="9" t="s">
+        <v>1851</v>
+      </c>
+      <c r="L1778" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:12" ht="30" customHeight="1">
+      <c r="A1779" s="3">
+        <v>1781</v>
+      </c>
+      <c r="B1779" s="5" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1779" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="D1779" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E1779" s="9" t="s">
+        <v>1850</v>
+      </c>
+      <c r="F1779" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1779" s="19">
+        <v>8.52</v>
+      </c>
+      <c r="I1779" s="20">
+        <v>8.52</v>
+      </c>
+      <c r="K1779" s="9" t="s">
+        <v>1852</v>
+      </c>
+      <c r="L1779" s="12">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1769"/>
+  <autoFilter ref="A1:L1779"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
